--- a/data/TX-123BT/Power_VRES.xlsx
+++ b/data/TX-123BT/Power_VRES.xlsx
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>1</v>
@@ -7109,7 +7109,7 @@
         <v>0.0001</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>1</v>
@@ -8204,7 +8204,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="13" t="n">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="13" t="n">
         <v>1</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>1</v>
@@ -18952,7 +18952,7 @@
         <v>0.0001</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>1</v>
@@ -20047,7 +20047,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="13" t="n">
         <v>1</v>
@@ -20631,7 +20631,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="13" t="n">
         <v>1</v>
@@ -28313,7 +28313,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>1</v>
@@ -30795,7 +30795,7 @@
         <v>0.0001</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>1</v>
@@ -31890,7 +31890,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="13" t="n">
         <v>1</v>
@@ -32474,7 +32474,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="13" t="n">
         <v>1</v>
@@ -40156,7 +40156,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>1</v>
@@ -42638,7 +42638,7 @@
         <v>0.0001</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>1</v>
@@ -43733,7 +43733,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="13" t="n">
         <v>1</v>
@@ -44317,7 +44317,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="13" t="n">
         <v>1</v>
@@ -51999,7 +51999,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="13" t="n">
         <v>1</v>
@@ -54481,7 +54481,7 @@
         <v>0.0001</v>
       </c>
       <c r="H87" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="13" t="n">
         <v>1</v>
@@ -55576,7 +55576,7 @@
         <v>0</v>
       </c>
       <c r="H102" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I102" s="13" t="n">
         <v>1</v>
@@ -56160,7 +56160,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" s="13" t="n">
         <v>1</v>
